--- a/Project-7 ---/V2/Data/cancer_data_fixed_v4.xlsx
+++ b/Project-7 ---/V2/Data/cancer_data_fixed_v4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
   <si>
     <t xml:space="preserve">mobile</t>
   </si>
@@ -474,7 +474,7 @@
     <t xml:space="preserve">Grade 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Biopsy</t>
+    <t xml:space="preserve">No Surgery</t>
   </si>
   <si>
     <t xml:space="preserve">1,5,6</t>
@@ -559,9 +559,6 @@
   </si>
   <si>
     <t xml:space="preserve">&gt;15000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Surgery</t>
   </si>
   <si>
     <t xml:space="preserve">Partial response</t>
@@ -3000,7 +2997,7 @@
         <v>116</v>
       </c>
       <c r="AT6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU6" t="s">
         <v>127</v>
@@ -3063,7 +3060,7 @@
         <v>134</v>
       </c>
       <c r="BS6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT6" t="s">
         <v>158</v>
@@ -3211,7 +3208,7 @@
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
         <v>118</v>
@@ -3328,7 +3325,7 @@
       <c r="BB7"/>
       <c r="BC7"/>
       <c r="BD7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BE7"/>
       <c r="BF7"/>
@@ -3363,7 +3360,7 @@
         <v>134</v>
       </c>
       <c r="BS7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT7" t="s">
         <v>158</v>
@@ -3371,7 +3368,7 @@
       <c r="BU7"/>
       <c r="BV7"/>
       <c r="BW7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX7" t="s">
         <v>130</v>
@@ -3511,7 +3508,7 @@
         <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H8" t="s">
         <v>118</v>
@@ -3575,7 +3572,7 @@
         <v>114</v>
       </c>
       <c r="AK8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL8" t="n">
         <v>3</v>
@@ -3587,13 +3584,13 @@
         <v>116</v>
       </c>
       <c r="AO8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AR8" t="s">
         <v>164</v>
@@ -3665,7 +3662,7 @@
         <v>134</v>
       </c>
       <c r="BS8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT8" t="s">
         <v>178</v>
@@ -3987,7 +3984,7 @@
       <c r="BU9"/>
       <c r="BV9"/>
       <c r="BW9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX9" t="s">
         <v>130</v>
@@ -4215,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="AQ10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AR10" t="s">
         <v>164</v>
@@ -4519,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="AQ11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AR11" t="s">
         <v>164</v>
@@ -4555,7 +4552,7 @@
         <v>116</v>
       </c>
       <c r="BE11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BF11" t="n">
         <v>18</v>
@@ -4605,7 +4602,7 @@
       <c r="BU11"/>
       <c r="BV11"/>
       <c r="BW11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX11" t="s">
         <v>131</v>
@@ -4695,7 +4692,7 @@
         <v>143</v>
       </c>
       <c r="DA11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB11" t="s">
         <v>130</v>
@@ -4869,7 +4866,7 @@
         <v>177</v>
       </c>
       <c r="BE12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BF12" t="n">
         <v>16</v>
@@ -4903,7 +4900,7 @@
         <v>116</v>
       </c>
       <c r="BQ12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BR12" t="s">
         <v>134</v>
@@ -5185,7 +5182,7 @@
         <v>177</v>
       </c>
       <c r="BE13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BF13" t="n">
         <v>14</v>
@@ -5227,7 +5224,7 @@
         <v>134</v>
       </c>
       <c r="BS13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT13" t="s">
         <v>158</v>
@@ -5235,7 +5232,7 @@
       <c r="BU13"/>
       <c r="BV13"/>
       <c r="BW13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX13" t="s">
         <v>130</v>
@@ -5431,7 +5428,7 @@
         <v>114</v>
       </c>
       <c r="AG14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH14"/>
       <c r="AI14"/>
@@ -5493,7 +5490,7 @@
         <v>177</v>
       </c>
       <c r="BE14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BF14" t="n">
         <v>18</v>
@@ -5666,7 +5663,7 @@
         <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E15" t="s">
         <v>116</v>
@@ -5675,7 +5672,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" t="s">
         <v>116</v>
@@ -5790,7 +5787,7 @@
       <c r="BB15"/>
       <c r="BC15"/>
       <c r="BD15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BE15"/>
       <c r="BF15"/>
@@ -5819,7 +5816,7 @@
         <v>116</v>
       </c>
       <c r="BQ15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BR15" t="s">
         <v>134</v>
@@ -5837,7 +5834,7 @@
         <v>24</v>
       </c>
       <c r="BW15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX15" t="s">
         <v>130</v>
@@ -6045,7 +6042,7 @@
         <v>114</v>
       </c>
       <c r="AK16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL16" t="n">
         <v>6</v>
@@ -6054,7 +6051,7 @@
         <v>116</v>
       </c>
       <c r="AN16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s">
         <v>152</v>
@@ -6070,7 +6067,7 @@
       </c>
       <c r="AS16"/>
       <c r="AT16" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU16" t="s">
         <v>127</v>
@@ -6229,13 +6226,13 @@
         <v>141</v>
       </c>
       <c r="CY16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CZ16" t="s">
         <v>143</v>
       </c>
       <c r="DA16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB16" t="s">
         <v>130</v>
@@ -6351,7 +6348,7 @@
         <v>114</v>
       </c>
       <c r="AK17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="n">
         <v>6</v>
@@ -6369,16 +6366,16 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="s">
+        <v>206</v>
+      </c>
+      <c r="AR17" t="s">
         <v>207</v>
       </c>
-      <c r="AR17" t="s">
-        <v>208</v>
-      </c>
       <c r="AS17" t="s">
         <v>116</v>
       </c>
       <c r="AT17" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU17" t="s">
         <v>127</v>
@@ -6405,7 +6402,7 @@
         <v>154</v>
       </c>
       <c r="BE17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BF17" t="n">
         <v>12</v>
@@ -6613,7 +6610,7 @@
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P18" t="s">
         <v>114</v>
@@ -6663,7 +6660,7 @@
         <v>114</v>
       </c>
       <c r="AK18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL18" t="n">
         <v>12</v>
@@ -6681,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR18" t="s">
         <v>164</v>
@@ -6690,7 +6687,7 @@
         <v>116</v>
       </c>
       <c r="AT18" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU18" t="s">
         <v>127</v>
@@ -6717,7 +6714,7 @@
         <v>150</v>
       </c>
       <c r="BE18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BF18" t="n">
         <v>8</v>
@@ -6763,7 +6760,7 @@
       <c r="BU18"/>
       <c r="BV18"/>
       <c r="BW18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX18" t="s">
         <v>130</v>
@@ -6963,7 +6960,7 @@
         <v>114</v>
       </c>
       <c r="AG19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AH19"/>
       <c r="AI19"/>
@@ -6971,7 +6968,7 @@
         <v>114</v>
       </c>
       <c r="AK19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="n">
         <v>12</v>
@@ -6983,13 +6980,13 @@
         <v>114</v>
       </c>
       <c r="AO19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AR19" t="s">
         <v>164</v>
@@ -6998,7 +6995,7 @@
         <v>116</v>
       </c>
       <c r="AT19" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU19" t="s">
         <v>127</v>
@@ -7073,7 +7070,7 @@
         <v>11</v>
       </c>
       <c r="BW19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX19" t="s">
         <v>130</v>
@@ -7281,7 +7278,7 @@
         <v>114</v>
       </c>
       <c r="AK20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="n">
         <v>3</v>
@@ -7299,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AR20" t="s">
         <v>164</v>
@@ -7381,7 +7378,7 @@
       <c r="BU20"/>
       <c r="BV20"/>
       <c r="BW20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX20" t="s">
         <v>131</v>
@@ -7579,7 +7576,7 @@
         <v>114</v>
       </c>
       <c r="AG21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AH21"/>
       <c r="AI21"/>
@@ -7647,7 +7644,7 @@
         <v>177</v>
       </c>
       <c r="BE21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BF21" t="n">
         <v>10</v>
@@ -7691,7 +7688,7 @@
       <c r="BU21"/>
       <c r="BV21"/>
       <c r="BW21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX21" t="s">
         <v>130</v>
@@ -7820,7 +7817,7 @@
         <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E22" t="s">
         <v>116</v>
@@ -7829,7 +7826,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H22" t="s">
         <v>116</v>
@@ -7862,7 +7859,7 @@
       <c r="V22"/>
       <c r="W22"/>
       <c r="X22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y22" t="n">
         <v>13</v>
@@ -7924,7 +7921,7 @@
         <v>116</v>
       </c>
       <c r="AT22" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU22" t="s">
         <v>127</v>
@@ -7951,7 +7948,7 @@
         <v>177</v>
       </c>
       <c r="BE22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BF22" t="n">
         <v>12</v>
@@ -8207,7 +8204,7 @@
         <v>114</v>
       </c>
       <c r="AK23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -8232,7 +8229,7 @@
       </c>
       <c r="AS23"/>
       <c r="AT23" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU23" t="s">
         <v>127</v>
@@ -8262,7 +8259,7 @@
         <v>114</v>
       </c>
       <c r="BD23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BE23" t="s">
         <v>167</v>
@@ -8315,7 +8312,7 @@
         <v>11</v>
       </c>
       <c r="BW23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX23" t="s">
         <v>131</v>
@@ -8405,7 +8402,7 @@
         <v>143</v>
       </c>
       <c r="DA23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB23" t="s">
         <v>130</v>
@@ -8446,7 +8443,7 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
         <v>116</v>
@@ -8455,7 +8452,7 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H24" t="s">
         <v>118</v>
@@ -8579,7 +8576,7 @@
         <v>177</v>
       </c>
       <c r="BE24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BF24" t="n">
         <v>12</v>
@@ -8609,7 +8606,7 @@
         <v>116</v>
       </c>
       <c r="BQ24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BR24" t="s">
         <v>134</v>
@@ -8833,7 +8830,7 @@
         <v>114</v>
       </c>
       <c r="AK25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL25" t="n">
         <v>24</v>
@@ -8845,7 +8842,7 @@
         <v>114</v>
       </c>
       <c r="AO25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP25" t="n">
         <v>0</v>
@@ -8858,7 +8855,7 @@
       </c>
       <c r="AS25"/>
       <c r="AT25" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU25" t="s">
         <v>127</v>
@@ -8885,7 +8882,7 @@
         <v>116</v>
       </c>
       <c r="BE25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BF25" t="n">
         <v>14</v>
@@ -9129,7 +9126,7 @@
         <v>114</v>
       </c>
       <c r="AG26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AH26"/>
       <c r="AI26"/>
@@ -9164,7 +9161,7 @@
         <v>116</v>
       </c>
       <c r="AT26" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU26" t="s">
         <v>127</v>
@@ -9188,10 +9185,10 @@
       <c r="BB26"/>
       <c r="BC26"/>
       <c r="BD26" t="s">
+        <v>222</v>
+      </c>
+      <c r="BE26" t="s">
         <v>223</v>
-      </c>
-      <c r="BE26" t="s">
-        <v>224</v>
       </c>
       <c r="BF26" t="n">
         <v>17</v>
@@ -9225,7 +9222,7 @@
         <v>116</v>
       </c>
       <c r="BQ26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BR26" t="s">
         <v>169</v>
@@ -9370,7 +9367,7 @@
         <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s">
         <v>116</v>
@@ -9414,7 +9411,7 @@
       <c r="V27"/>
       <c r="W27"/>
       <c r="X27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y27" t="n">
         <v>13</v>
@@ -9449,7 +9446,7 @@
         <v>114</v>
       </c>
       <c r="AK27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AL27" t="n">
         <v>6</v>
@@ -9474,7 +9471,7 @@
       </c>
       <c r="AS27"/>
       <c r="AT27" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU27" t="s">
         <v>127</v>
@@ -9639,7 +9636,7 @@
         <v>143</v>
       </c>
       <c r="DA27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB27" t="s">
         <v>130</v>
@@ -9755,7 +9752,7 @@
         <v>114</v>
       </c>
       <c r="AK28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AL28" t="n">
         <v>18</v>
@@ -9773,7 +9770,7 @@
         <v>2</v>
       </c>
       <c r="AQ28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AR28" t="s">
         <v>164</v>
@@ -9782,7 +9779,7 @@
         <v>116</v>
       </c>
       <c r="AT28" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU28" t="s">
         <v>127</v>
@@ -9859,7 +9856,7 @@
         <v>10</v>
       </c>
       <c r="BW28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX28" t="s">
         <v>131</v>
@@ -10069,7 +10066,7 @@
         <v>114</v>
       </c>
       <c r="AK29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AL29" t="n">
         <v>6</v>
@@ -10175,7 +10172,7 @@
         <v>11</v>
       </c>
       <c r="BW29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX29" t="s">
         <v>130</v>
@@ -10265,7 +10262,7 @@
         <v>143</v>
       </c>
       <c r="DA29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB29" t="s">
         <v>130</v>
@@ -10379,7 +10376,7 @@
         <v>114</v>
       </c>
       <c r="AK30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AL30" t="n">
         <v>6</v>
@@ -10404,7 +10401,7 @@
       </c>
       <c r="AS30"/>
       <c r="AT30" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU30" t="s">
         <v>127</v>
@@ -10431,7 +10428,7 @@
         <v>116</v>
       </c>
       <c r="BE30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BF30" t="n">
         <v>9</v>
@@ -10638,7 +10635,7 @@
       </c>
       <c r="M31"/>
       <c r="N31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O31" t="s">
         <v>120</v>
@@ -10687,7 +10684,7 @@
         <v>114</v>
       </c>
       <c r="AK31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AL31" t="n">
         <v>3</v>
@@ -10795,7 +10792,7 @@
         <v>10</v>
       </c>
       <c r="BW31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX31" t="s">
         <v>131</v>
@@ -10926,7 +10923,7 @@
         <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E32" t="s">
         <v>116</v>
@@ -10935,7 +10932,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s">
         <v>124</v>
@@ -10999,7 +10996,7 @@
         <v>114</v>
       </c>
       <c r="AK32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL32" t="n">
         <v>12</v>
@@ -11017,14 +11014,14 @@
         <v>3</v>
       </c>
       <c r="AQ32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR32" t="s">
         <v>164</v>
       </c>
       <c r="AS32"/>
       <c r="AT32" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU32" t="s">
         <v>127</v>
@@ -11101,7 +11098,7 @@
         <v>7</v>
       </c>
       <c r="BW32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX32" t="s">
         <v>131</v>
@@ -11257,7 +11254,7 @@
       <c r="M33"/>
       <c r="N33"/>
       <c r="O33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P33" t="s">
         <v>114</v>
@@ -11272,7 +11269,7 @@
       <c r="V33"/>
       <c r="W33"/>
       <c r="X33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
@@ -11330,7 +11327,7 @@
         <v>116</v>
       </c>
       <c r="AT33" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU33" t="s">
         <v>127</v>
@@ -11354,10 +11351,10 @@
       <c r="BB33"/>
       <c r="BC33"/>
       <c r="BD33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BE33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BF33" t="n">
         <v>16</v>
@@ -11370,7 +11367,7 @@
         <v>168</v>
       </c>
       <c r="BJ33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BK33" t="s">
         <v>114</v>
@@ -11407,7 +11404,7 @@
         <v>19</v>
       </c>
       <c r="BW33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX33" t="s">
         <v>130</v>
@@ -11497,7 +11494,7 @@
         <v>143</v>
       </c>
       <c r="DA33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB33" t="s">
         <v>130</v>
@@ -11615,7 +11612,7 @@
         <v>114</v>
       </c>
       <c r="AK34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL34" t="n">
         <v>2</v>
@@ -11640,7 +11637,7 @@
       </c>
       <c r="AS34"/>
       <c r="AT34" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU34" t="s">
         <v>127</v>
@@ -11875,7 +11872,7 @@
       <c r="M35"/>
       <c r="N35"/>
       <c r="O35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P35" t="s">
         <v>114</v>
@@ -11927,7 +11924,7 @@
         <v>114</v>
       </c>
       <c r="AK35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL35" t="n">
         <v>2</v>
@@ -12137,7 +12134,7 @@
         <v>173</v>
       </c>
       <c r="DE35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF35" t="s">
         <v>130</v>
@@ -12255,14 +12252,14 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AR36" t="s">
         <v>125</v>
       </c>
       <c r="AS36"/>
       <c r="AT36" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU36" t="s">
         <v>127</v>
@@ -12286,10 +12283,10 @@
       <c r="BB36"/>
       <c r="BC36"/>
       <c r="BD36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BE36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BF36" t="n">
         <v>16</v>
@@ -12423,7 +12420,7 @@
         <v>143</v>
       </c>
       <c r="DA36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB36" t="s">
         <v>131</v>
@@ -12557,14 +12554,14 @@
         <v>1</v>
       </c>
       <c r="AQ37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AR37" t="s">
         <v>125</v>
       </c>
       <c r="AS37"/>
       <c r="AT37" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU37" t="s">
         <v>127</v>
@@ -12606,7 +12603,7 @@
         <v>168</v>
       </c>
       <c r="BJ37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BK37" t="s">
         <v>114</v>
@@ -12639,7 +12636,7 @@
       <c r="BU37"/>
       <c r="BV37"/>
       <c r="BW37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX37" t="s">
         <v>130</v>
@@ -12868,7 +12865,7 @@
         <v>116</v>
       </c>
       <c r="AT38" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU38" t="s">
         <v>127</v>
@@ -12925,7 +12922,7 @@
         <v>116</v>
       </c>
       <c r="BQ38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BR38" t="s">
         <v>134</v>
@@ -12939,7 +12936,7 @@
       <c r="BU38"/>
       <c r="BV38"/>
       <c r="BW38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX38" t="s">
         <v>130</v>
@@ -13023,7 +13020,7 @@
         <v>141</v>
       </c>
       <c r="CY38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CZ38" t="s">
         <v>143</v>
@@ -13145,7 +13142,7 @@
         <v>114</v>
       </c>
       <c r="AK39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL39" t="n">
         <v>12</v>
@@ -13163,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="AQ39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AR39" t="s">
         <v>164</v>
@@ -13200,7 +13197,7 @@
         <v>116</v>
       </c>
       <c r="BD39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BE39" t="s">
         <v>124</v>
@@ -13247,7 +13244,7 @@
       <c r="BU39"/>
       <c r="BV39"/>
       <c r="BW39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX39" t="s">
         <v>131</v>
@@ -13337,7 +13334,7 @@
         <v>143</v>
       </c>
       <c r="DA39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB39" t="s">
         <v>131</v>
@@ -13349,7 +13346,7 @@
         <v>145</v>
       </c>
       <c r="DE39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF39" t="s">
         <v>130</v>
@@ -13378,7 +13375,7 @@
         <v>114</v>
       </c>
       <c r="D40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E40" t="s">
         <v>116</v>
@@ -13387,7 +13384,7 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H40" t="s">
         <v>116</v>
@@ -13416,7 +13413,7 @@
         <v>118</v>
       </c>
       <c r="R40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S40"/>
       <c r="T40" t="s">
@@ -13457,7 +13454,7 @@
         <v>114</v>
       </c>
       <c r="AK40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL40" t="n">
         <v>1</v>
@@ -13506,7 +13503,7 @@
       <c r="BB40"/>
       <c r="BC40"/>
       <c r="BD40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BE40" t="s">
         <v>114</v>
@@ -13553,7 +13550,7 @@
       <c r="BU40"/>
       <c r="BV40"/>
       <c r="BW40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX40" t="s">
         <v>130</v>
@@ -13684,7 +13681,7 @@
         <v>114</v>
       </c>
       <c r="D41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
         <v>116</v>
@@ -13757,7 +13754,7 @@
         <v>114</v>
       </c>
       <c r="AK41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AL41" t="n">
         <v>3</v>
@@ -13775,7 +13772,7 @@
         <v>2</v>
       </c>
       <c r="AQ41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR41" t="s">
         <v>164</v>
@@ -13784,7 +13781,7 @@
         <v>116</v>
       </c>
       <c r="AT41" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU41" t="s">
         <v>127</v>
@@ -13808,7 +13805,7 @@
       <c r="BB41"/>
       <c r="BC41"/>
       <c r="BD41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BE41" t="s">
         <v>167</v>
@@ -13861,7 +13858,7 @@
         <v>15</v>
       </c>
       <c r="BW41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX41" t="s">
         <v>131</v>
@@ -13945,13 +13942,13 @@
         <v>141</v>
       </c>
       <c r="CY41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="CZ41" t="s">
         <v>143</v>
       </c>
       <c r="DA41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB41" t="s">
         <v>130</v>
@@ -13992,7 +13989,7 @@
         <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
         <v>116</v>
@@ -14071,7 +14068,7 @@
         <v>114</v>
       </c>
       <c r="AK42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL42" t="n">
         <v>8</v>
@@ -14089,14 +14086,14 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR42" t="s">
         <v>164</v>
       </c>
       <c r="AS42"/>
       <c r="AT42" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU42" t="s">
         <v>127</v>
@@ -14302,7 +14299,7 @@
         <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E43" t="s">
         <v>116</v>
@@ -14406,7 +14403,7 @@
         <v>116</v>
       </c>
       <c r="AT43" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU43" t="s">
         <v>127</v>
@@ -14430,10 +14427,10 @@
       <c r="BB43"/>
       <c r="BC43"/>
       <c r="BD43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BE43" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BF43" t="n">
         <v>18</v>
@@ -14477,7 +14474,7 @@
       <c r="BU43"/>
       <c r="BV43"/>
       <c r="BW43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX43" t="s">
         <v>130</v>
@@ -14567,7 +14564,7 @@
         <v>143</v>
       </c>
       <c r="DA43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB43" t="s">
         <v>130</v>
@@ -14679,7 +14676,7 @@
         <v>114</v>
       </c>
       <c r="AK44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL44" t="n">
         <v>12</v>
@@ -14731,7 +14728,7 @@
         <v>116</v>
       </c>
       <c r="BE44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BF44" t="n">
         <v>10</v>
@@ -14912,7 +14909,7 @@
         <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E45" t="s">
         <v>116</v>
@@ -14938,7 +14935,7 @@
       </c>
       <c r="M45"/>
       <c r="N45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O45" t="s">
         <v>120</v>
@@ -14991,7 +14988,7 @@
         <v>114</v>
       </c>
       <c r="AK45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL45" t="n">
         <v>6</v>
@@ -15016,7 +15013,7 @@
       </c>
       <c r="AS45"/>
       <c r="AT45" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU45" t="s">
         <v>127</v>
@@ -15043,7 +15040,7 @@
         <v>116</v>
       </c>
       <c r="BE45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BF45" t="n">
         <v>12</v>
@@ -15079,7 +15076,7 @@
         <v>134</v>
       </c>
       <c r="BS45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT45" t="s">
         <v>158</v>
@@ -15087,7 +15084,7 @@
       <c r="BU45"/>
       <c r="BV45"/>
       <c r="BW45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX45" t="s">
         <v>130</v>
@@ -15218,7 +15215,7 @@
         <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E46" t="s">
         <v>116</v>
@@ -15348,10 +15345,10 @@
         <v>114</v>
       </c>
       <c r="BD46" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BE46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BF46" t="n">
         <v>12</v>
@@ -15381,13 +15378,13 @@
         <v>116</v>
       </c>
       <c r="BQ46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BR46" t="s">
         <v>134</v>
       </c>
       <c r="BS46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT46" t="s">
         <v>158</v>
@@ -15599,7 +15596,7 @@
         <v>114</v>
       </c>
       <c r="AK47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AL47" t="n">
         <v>24</v>
@@ -15617,14 +15614,14 @@
         <v>2</v>
       </c>
       <c r="AQ47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR47" t="s">
         <v>164</v>
       </c>
       <c r="AS47"/>
       <c r="AT47" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU47" t="s">
         <v>127</v>
@@ -15651,7 +15648,7 @@
         <v>116</v>
       </c>
       <c r="BE47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BF47" t="n">
         <v>12</v>
@@ -15701,7 +15698,7 @@
         <v>12</v>
       </c>
       <c r="BW47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX47" t="s">
         <v>131</v>
@@ -15791,7 +15788,7 @@
         <v>143</v>
       </c>
       <c r="DA47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB47" t="s">
         <v>130</v>
@@ -15921,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR48" t="s">
         <v>164</v>
@@ -16011,7 +16008,7 @@
         <v>14</v>
       </c>
       <c r="BW48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX48" t="s">
         <v>131</v>
@@ -16142,7 +16139,7 @@
         <v>114</v>
       </c>
       <c r="D49" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
         <v>116</v>
@@ -16151,7 +16148,7 @@
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H49" t="s">
         <v>118</v>
@@ -16215,7 +16212,7 @@
         <v>114</v>
       </c>
       <c r="AK49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL49" t="n">
         <v>36</v>
@@ -16233,7 +16230,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR49" t="s">
         <v>164</v>
@@ -16242,7 +16239,7 @@
         <v>116</v>
       </c>
       <c r="AT49" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU49" t="s">
         <v>127</v>
@@ -16266,7 +16263,7 @@
       <c r="BB49"/>
       <c r="BC49"/>
       <c r="BD49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BE49" t="s">
         <v>155</v>
@@ -16299,13 +16296,13 @@
         <v>116</v>
       </c>
       <c r="BQ49" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BR49" t="s">
         <v>134</v>
       </c>
       <c r="BS49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT49" t="s">
         <v>158</v>
@@ -16313,7 +16310,7 @@
       <c r="BU49"/>
       <c r="BV49"/>
       <c r="BW49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX49" t="s">
         <v>130</v>
@@ -16517,7 +16514,7 @@
         <v>114</v>
       </c>
       <c r="AK50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL50" t="n">
         <v>6</v>
@@ -16535,14 +16532,14 @@
         <v>2</v>
       </c>
       <c r="AQ50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR50" t="s">
         <v>164</v>
       </c>
       <c r="AS50"/>
       <c r="AT50" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU50" t="s">
         <v>127</v>
@@ -16575,7 +16572,7 @@
         <v>116</v>
       </c>
       <c r="BE50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BF50" t="n">
         <v>8</v>
@@ -16711,7 +16708,7 @@
         <v>143</v>
       </c>
       <c r="DA50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB50" t="s">
         <v>130</v>
@@ -16723,7 +16720,7 @@
         <v>173</v>
       </c>
       <c r="DE50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF50" t="s">
         <v>130</v>
@@ -16831,7 +16828,7 @@
         <v>114</v>
       </c>
       <c r="AK51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL51" t="n">
         <v>18</v>
@@ -16840,7 +16837,7 @@
         <v>116</v>
       </c>
       <c r="AN51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AO51" t="s">
         <v>152</v>
@@ -16933,7 +16930,7 @@
       <c r="BU51"/>
       <c r="BV51"/>
       <c r="BW51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX51" t="s">
         <v>130</v>
@@ -17017,7 +17014,7 @@
         <v>141</v>
       </c>
       <c r="CY51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CZ51" t="s">
         <v>143</v>
@@ -17137,7 +17134,7 @@
         <v>114</v>
       </c>
       <c r="AK52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL52" t="n">
         <v>24</v>
@@ -17195,7 +17192,7 @@
         <v>116</v>
       </c>
       <c r="BE52" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BF52" t="n">
         <v>12</v>
@@ -17231,7 +17228,7 @@
         <v>134</v>
       </c>
       <c r="BS52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT52" t="s">
         <v>158</v>
@@ -17239,7 +17236,7 @@
       <c r="BU52"/>
       <c r="BV52"/>
       <c r="BW52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX52" t="s">
         <v>131</v>
@@ -17406,7 +17403,7 @@
         <v>155</v>
       </c>
       <c r="R53" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -17451,7 +17448,7 @@
         <v>114</v>
       </c>
       <c r="AK53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AL53" t="n">
         <v>12</v>
@@ -17500,10 +17497,10 @@
       <c r="BB53"/>
       <c r="BC53"/>
       <c r="BD53" t="s">
+        <v>245</v>
+      </c>
+      <c r="BE53" t="s">
         <v>246</v>
-      </c>
-      <c r="BE53" t="s">
-        <v>247</v>
       </c>
       <c r="BF53" t="n">
         <v>8</v>
@@ -17539,7 +17536,7 @@
         <v>134</v>
       </c>
       <c r="BS53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT53" t="s">
         <v>158</v>
@@ -17547,7 +17544,7 @@
       <c r="BU53"/>
       <c r="BV53"/>
       <c r="BW53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX53" t="s">
         <v>131</v>
@@ -17755,7 +17752,7 @@
         <v>114</v>
       </c>
       <c r="AK54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL54" t="n">
         <v>4</v>
@@ -17773,7 +17770,7 @@
         <v>1</v>
       </c>
       <c r="AQ54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AR54" t="s">
         <v>164</v>
@@ -17782,7 +17779,7 @@
         <v>116</v>
       </c>
       <c r="AT54" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU54" t="s">
         <v>127</v>
@@ -17859,7 +17856,7 @@
         <v>10</v>
       </c>
       <c r="BW54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX54" t="s">
         <v>131</v>
@@ -17988,7 +17985,7 @@
         <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E55" t="s">
         <v>116</v>
@@ -18061,7 +18058,7 @@
         <v>114</v>
       </c>
       <c r="AK55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL55" t="n">
         <v>18</v>
@@ -18079,7 +18076,7 @@
         <v>0</v>
       </c>
       <c r="AQ55" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR55" t="s">
         <v>164</v>
@@ -18118,10 +18115,10 @@
         <v>114</v>
       </c>
       <c r="BD55" t="s">
+        <v>248</v>
+      </c>
+      <c r="BE55" t="s">
         <v>249</v>
-      </c>
-      <c r="BE55" t="s">
-        <v>250</v>
       </c>
       <c r="BF55" t="n">
         <v>16</v>
@@ -18165,7 +18162,7 @@
       <c r="BU55"/>
       <c r="BV55"/>
       <c r="BW55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX55" t="s">
         <v>130</v>
@@ -18255,7 +18252,7 @@
         <v>143</v>
       </c>
       <c r="DA55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB55" t="s">
         <v>130</v>
@@ -18373,7 +18370,7 @@
         <v>114</v>
       </c>
       <c r="AK56" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AL56" t="n">
         <v>30</v>
@@ -18583,7 +18580,7 @@
         <v>173</v>
       </c>
       <c r="DE56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF56" t="s">
         <v>130</v>
@@ -18625,7 +18622,7 @@
         <v>118</v>
       </c>
       <c r="I57" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J57"/>
       <c r="K57" t="s">
@@ -18685,7 +18682,7 @@
         <v>114</v>
       </c>
       <c r="AK57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL57" t="n">
         <v>24</v>
@@ -18694,7 +18691,7 @@
         <v>116</v>
       </c>
       <c r="AN57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AO57" t="s">
         <v>152</v>
@@ -18710,7 +18707,7 @@
       </c>
       <c r="AS57"/>
       <c r="AT57" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU57" t="s">
         <v>127</v>
@@ -18737,7 +18734,7 @@
         <v>116</v>
       </c>
       <c r="BE57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BF57" t="n">
         <v>22</v>
@@ -18779,7 +18776,7 @@
       <c r="BU57"/>
       <c r="BV57"/>
       <c r="BW57" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX57" t="s">
         <v>130</v>
@@ -18863,7 +18860,7 @@
         <v>141</v>
       </c>
       <c r="CY57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CZ57" t="s">
         <v>171</v>
@@ -18981,7 +18978,7 @@
         <v>114</v>
       </c>
       <c r="AK58" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AL58" t="n">
         <v>18</v>
@@ -19006,7 +19003,7 @@
       </c>
       <c r="AS58"/>
       <c r="AT58" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU58" t="s">
         <v>127</v>
@@ -19039,7 +19036,7 @@
         <v>116</v>
       </c>
       <c r="BE58" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="BF58" t="n">
         <v>12</v>
@@ -19091,7 +19088,7 @@
         <v>6</v>
       </c>
       <c r="BW58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX58" t="s">
         <v>130</v>
@@ -19181,7 +19178,7 @@
         <v>143</v>
       </c>
       <c r="DA58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB58" t="s">
         <v>130</v>
@@ -19193,7 +19190,7 @@
         <v>173</v>
       </c>
       <c r="DE58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF58" t="s">
         <v>130</v>
@@ -19237,7 +19234,7 @@
         <v>118</v>
       </c>
       <c r="I59" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J59"/>
       <c r="K59" t="s">
@@ -19304,7 +19301,7 @@
         <v>116</v>
       </c>
       <c r="AN59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AO59" t="s">
         <v>152</v>
@@ -19313,7 +19310,7 @@
         <v>1</v>
       </c>
       <c r="AQ59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AR59" t="s">
         <v>164</v>
@@ -19352,10 +19349,10 @@
         <v>116</v>
       </c>
       <c r="BD59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BE59" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="BF59" t="n">
         <v>18</v>
@@ -19403,7 +19400,7 @@
       <c r="BU59"/>
       <c r="BV59"/>
       <c r="BW59" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX59" t="s">
         <v>130</v>
@@ -19487,7 +19484,7 @@
         <v>141</v>
       </c>
       <c r="CY59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CZ59" t="s">
         <v>143</v>
@@ -19505,7 +19502,7 @@
         <v>173</v>
       </c>
       <c r="DE59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF59" t="s">
         <v>130</v>
@@ -19547,7 +19544,7 @@
         <v>118</v>
       </c>
       <c r="I60" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J60"/>
       <c r="K60" t="s">
@@ -19609,7 +19606,7 @@
         <v>114</v>
       </c>
       <c r="AK60" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AL60" t="n">
         <v>24</v>
@@ -19667,7 +19664,7 @@
         <v>116</v>
       </c>
       <c r="BE60" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF60" t="n">
         <v>22</v>
@@ -19815,7 +19812,7 @@
         <v>145</v>
       </c>
       <c r="DE60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF60" t="s">
         <v>130</v>
@@ -19859,7 +19856,7 @@
         <v>118</v>
       </c>
       <c r="I61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J61"/>
       <c r="K61" t="s">
@@ -19921,7 +19918,7 @@
         <v>114</v>
       </c>
       <c r="AK61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL61" t="n">
         <v>18</v>
@@ -19979,7 +19976,7 @@
         <v>116</v>
       </c>
       <c r="BE61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BF61" t="n">
         <v>20</v>
@@ -20129,7 +20126,7 @@
         <v>173</v>
       </c>
       <c r="DE61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF61" t="s">
         <v>130</v>
@@ -20288,7 +20285,7 @@
         <v>116</v>
       </c>
       <c r="BD62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BE62" t="s">
         <v>167</v>
@@ -20341,7 +20338,7 @@
         <v>12</v>
       </c>
       <c r="BW62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX62" t="s">
         <v>130</v>
@@ -20431,7 +20428,7 @@
         <v>143</v>
       </c>
       <c r="DA62" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB62" t="s">
         <v>130</v>
@@ -20443,7 +20440,7 @@
         <v>173</v>
       </c>
       <c r="DE62" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF62" t="s">
         <v>130</v>
@@ -20607,7 +20604,7 @@
         <v>177</v>
       </c>
       <c r="BE63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BF63" t="n">
         <v>15</v>
@@ -20649,7 +20646,7 @@
       <c r="BU63"/>
       <c r="BV63"/>
       <c r="BW63" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX63" t="s">
         <v>130</v>
@@ -20853,7 +20850,7 @@
         <v>114</v>
       </c>
       <c r="AK64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL64" t="n">
         <v>30</v>
@@ -21047,7 +21044,7 @@
         <v>143</v>
       </c>
       <c r="DA64" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB64" t="s">
         <v>130</v>
@@ -21086,7 +21083,7 @@
         <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E65" t="s">
         <v>116</v>
@@ -21159,7 +21156,7 @@
         <v>114</v>
       </c>
       <c r="AK65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL65" t="n">
         <v>24</v>
@@ -21261,7 +21258,7 @@
       <c r="BU65"/>
       <c r="BV65"/>
       <c r="BW65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX65" t="s">
         <v>130</v>
@@ -21351,7 +21348,7 @@
         <v>143</v>
       </c>
       <c r="DA65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB65" t="s">
         <v>130</v>
@@ -21485,7 +21482,7 @@
         <v>0</v>
       </c>
       <c r="AQ66" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AR66" t="s">
         <v>125</v>
@@ -21555,7 +21552,7 @@
         <v>134</v>
       </c>
       <c r="BS66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT66" t="s">
         <v>158</v>
@@ -21769,7 +21766,7 @@
         <v>114</v>
       </c>
       <c r="AK67" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL67" t="n">
         <v>12</v>
@@ -21787,7 +21784,7 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR67" t="s">
         <v>164</v>
@@ -21796,7 +21793,7 @@
         <v>116</v>
       </c>
       <c r="AT67" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU67" t="s">
         <v>127</v>
@@ -21820,10 +21817,10 @@
       <c r="BB67"/>
       <c r="BC67"/>
       <c r="BD67" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="BE67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF67" t="n">
         <v>20</v>
@@ -21869,7 +21866,7 @@
       <c r="BU67"/>
       <c r="BV67"/>
       <c r="BW67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX67" t="s">
         <v>130</v>
@@ -22133,7 +22130,7 @@
         <v>177</v>
       </c>
       <c r="BE68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BF68" t="n">
         <v>20</v>
@@ -22175,7 +22172,7 @@
         <v>134</v>
       </c>
       <c r="BS68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT68" t="s">
         <v>158</v>
@@ -22387,7 +22384,7 @@
         <v>114</v>
       </c>
       <c r="AK69" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL69" t="n">
         <v>24</v>
@@ -22399,7 +22396,7 @@
         <v>114</v>
       </c>
       <c r="AO69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP69" t="n">
         <v>1</v>
@@ -22445,7 +22442,7 @@
         <v>116</v>
       </c>
       <c r="BE69" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BF69" t="n">
         <v>18</v>
@@ -22493,7 +22490,7 @@
       <c r="BU69"/>
       <c r="BV69"/>
       <c r="BW69" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX69" t="s">
         <v>131</v>
@@ -22583,7 +22580,7 @@
         <v>143</v>
       </c>
       <c r="DA69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB69" t="s">
         <v>130</v>
@@ -22697,7 +22694,7 @@
         <v>114</v>
       </c>
       <c r="AK70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AL70" t="n">
         <v>12</v>
@@ -22715,14 +22712,14 @@
         <v>1</v>
       </c>
       <c r="AQ70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AR70" t="s">
         <v>164</v>
       </c>
       <c r="AS70"/>
       <c r="AT70" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU70" t="s">
         <v>127</v>
@@ -22805,7 +22802,7 @@
         <v>12</v>
       </c>
       <c r="BW70" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX70" t="s">
         <v>130</v>
@@ -22907,7 +22904,7 @@
         <v>173</v>
       </c>
       <c r="DE70" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF70" t="s">
         <v>130</v>
@@ -23013,7 +23010,7 @@
         <v>114</v>
       </c>
       <c r="AK71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AL71" t="n">
         <v>18</v>
@@ -23031,7 +23028,7 @@
         <v>2</v>
       </c>
       <c r="AQ71" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR71" t="s">
         <v>164</v>
@@ -23073,7 +23070,7 @@
         <v>177</v>
       </c>
       <c r="BE71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BF71" t="n">
         <v>12</v>
@@ -23121,7 +23118,7 @@
       <c r="BU71"/>
       <c r="BV71"/>
       <c r="BW71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX71" t="s">
         <v>130</v>
@@ -23211,7 +23208,7 @@
         <v>143</v>
       </c>
       <c r="DA71" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB71" t="s">
         <v>130</v>
@@ -23223,7 +23220,7 @@
         <v>173</v>
       </c>
       <c r="DE71" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF71" t="s">
         <v>130</v>
@@ -23327,7 +23324,7 @@
         <v>114</v>
       </c>
       <c r="AK72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL72" t="n">
         <v>24</v>
@@ -23533,7 +23530,7 @@
         <v>145</v>
       </c>
       <c r="DE72" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF72" t="s">
         <v>130</v>
@@ -23569,7 +23566,7 @@
         <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H73" t="s">
         <v>118</v>
@@ -23649,7 +23646,7 @@
         <v>114</v>
       </c>
       <c r="AO73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP73" t="n">
         <v>0</v>
@@ -23737,7 +23734,7 @@
       <c r="BU73"/>
       <c r="BV73"/>
       <c r="BW73" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX73" t="s">
         <v>130</v>
@@ -23883,7 +23880,7 @@
         <v>118</v>
       </c>
       <c r="I74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J74"/>
       <c r="K74" t="s">
@@ -23947,7 +23944,7 @@
         <v>114</v>
       </c>
       <c r="AK74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL74" t="n">
         <v>24</v>
@@ -23965,7 +23962,7 @@
         <v>2</v>
       </c>
       <c r="AQ74" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AR74" t="s">
         <v>164</v>
@@ -24057,7 +24054,7 @@
         <v>12</v>
       </c>
       <c r="BW74" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX74" t="s">
         <v>131</v>
@@ -24147,7 +24144,7 @@
         <v>143</v>
       </c>
       <c r="DA74" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB74" t="s">
         <v>130</v>
@@ -24197,7 +24194,7 @@
         <v>18</v>
       </c>
       <c r="G75" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H75" t="s">
         <v>118</v>
@@ -24277,7 +24274,7 @@
         <v>116</v>
       </c>
       <c r="AO75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP75" t="n">
         <v>0</v>
@@ -24322,7 +24319,7 @@
         <v>116</v>
       </c>
       <c r="BD75" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BE75"/>
       <c r="BF75"/>
@@ -24359,7 +24356,7 @@
         <v>134</v>
       </c>
       <c r="BS75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT75" t="s">
         <v>158</v>
@@ -24367,7 +24364,7 @@
       <c r="BU75"/>
       <c r="BV75"/>
       <c r="BW75" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX75" t="s">
         <v>130</v>
@@ -24469,7 +24466,7 @@
         <v>145</v>
       </c>
       <c r="DE75" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF75" t="s">
         <v>130</v>
@@ -24496,7 +24493,7 @@
         <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E76" t="s">
         <v>116</v>
@@ -24505,7 +24502,7 @@
         <v>18</v>
       </c>
       <c r="G76" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H76" t="s">
         <v>118</v>
@@ -24589,10 +24586,10 @@
         <v>2</v>
       </c>
       <c r="AQ76" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AR76" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS76"/>
       <c r="AT76" t="s">
@@ -24620,7 +24617,7 @@
       <c r="BB76"/>
       <c r="BC76"/>
       <c r="BD76" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BE76" t="s">
         <v>124</v>
@@ -24669,7 +24666,7 @@
         <v>10</v>
       </c>
       <c r="BW76" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX76" t="s">
         <v>131</v>
@@ -24759,7 +24756,7 @@
         <v>143</v>
       </c>
       <c r="DA76" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB76" t="s">
         <v>130</v>
@@ -24800,7 +24797,7 @@
         <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E77" t="s">
         <v>116</v>
@@ -24924,7 +24921,7 @@
       <c r="BB77"/>
       <c r="BC77"/>
       <c r="BD77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BE77" t="s">
         <v>116</v>
@@ -24965,7 +24962,7 @@
         <v>134</v>
       </c>
       <c r="BS77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT77" t="s">
         <v>158</v>
@@ -24973,7 +24970,7 @@
       <c r="BU77"/>
       <c r="BV77"/>
       <c r="BW77" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX77" t="s">
         <v>130</v>
@@ -25063,7 +25060,7 @@
         <v>143</v>
       </c>
       <c r="DA77" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB77" t="s">
         <v>130</v>
@@ -25179,7 +25176,7 @@
         <v>114</v>
       </c>
       <c r="AK78" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL78" t="n">
         <v>24</v>
@@ -25287,7 +25284,7 @@
         <v>8</v>
       </c>
       <c r="BW78" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX78" t="s">
         <v>131</v>
@@ -25511,7 +25508,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AR79" t="s">
         <v>164</v>
@@ -25553,7 +25550,7 @@
         <v>177</v>
       </c>
       <c r="BE79" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="BF79" t="n">
         <v>12</v>
@@ -25689,7 +25686,7 @@
         <v>143</v>
       </c>
       <c r="DA79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB79" t="s">
         <v>130</v>
@@ -25701,7 +25698,7 @@
         <v>145</v>
       </c>
       <c r="DE79" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF79" t="s">
         <v>130</v>
@@ -25907,7 +25904,7 @@
       <c r="BU80"/>
       <c r="BV80"/>
       <c r="BW80" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX80" t="s">
         <v>130</v>
@@ -25997,7 +25994,7 @@
         <v>143</v>
       </c>
       <c r="DA80" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB80" t="s">
         <v>130</v>
@@ -26045,7 +26042,7 @@
         <v>18</v>
       </c>
       <c r="G81" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H81" t="s">
         <v>118</v>
@@ -26215,7 +26212,7 @@
       <c r="BU81"/>
       <c r="BV81"/>
       <c r="BW81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX81" t="s">
         <v>130</v>
@@ -26305,7 +26302,7 @@
         <v>143</v>
       </c>
       <c r="DA81" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB81" t="s">
         <v>130</v>
@@ -26431,7 +26428,7 @@
         <v>116</v>
       </c>
       <c r="AO82" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -26477,7 +26474,7 @@
         <v>116</v>
       </c>
       <c r="BE82" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BF82" t="n">
         <v>12</v>
@@ -26729,7 +26726,7 @@
         <v>114</v>
       </c>
       <c r="AK83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL83" t="n">
         <v>12</v>
@@ -26787,7 +26784,7 @@
         <v>116</v>
       </c>
       <c r="BE83" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BF83" t="n">
         <v>15</v>
@@ -26964,7 +26961,7 @@
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E84" t="s">
         <v>116</v>
@@ -26991,7 +26988,7 @@
       <c r="M84"/>
       <c r="N84"/>
       <c r="O84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P84" t="s">
         <v>114</v>
@@ -27041,7 +27038,7 @@
         <v>114</v>
       </c>
       <c r="AK84" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL84" t="n">
         <v>48</v>
@@ -27099,7 +27096,7 @@
         <v>116</v>
       </c>
       <c r="BE84" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BF84" t="n">
         <v>6</v>
@@ -27137,7 +27134,7 @@
         <v>134</v>
       </c>
       <c r="BS84" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT84" t="s">
         <v>158</v>
@@ -27145,7 +27142,7 @@
       <c r="BU84"/>
       <c r="BV84"/>
       <c r="BW84" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX84" t="s">
         <v>131</v>
@@ -27235,7 +27232,7 @@
         <v>143</v>
       </c>
       <c r="DA84" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB84" t="s">
         <v>130</v>
@@ -27247,7 +27244,7 @@
         <v>145</v>
       </c>
       <c r="DE84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF84" t="s">
         <v>130</v>
@@ -27371,10 +27368,10 @@
         <v>0</v>
       </c>
       <c r="AQ85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AR85" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS85" t="s">
         <v>116</v>
@@ -27413,7 +27410,7 @@
         <v>114</v>
       </c>
       <c r="BE85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="BF85" t="n">
         <v>30</v>
@@ -27559,7 +27556,7 @@
         <v>173</v>
       </c>
       <c r="DE85" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF85" t="s">
         <v>130</v>
@@ -27588,7 +27585,7 @@
         <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E86" t="s">
         <v>116</v>
@@ -27597,7 +27594,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H86" t="s">
         <v>118</v>
@@ -27692,7 +27689,7 @@
         <v>116</v>
       </c>
       <c r="AT86" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU86" t="s">
         <v>127</v>
@@ -28079,7 +28076,7 @@
       <c r="BU87"/>
       <c r="BV87"/>
       <c r="BW87" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX87" t="s">
         <v>130</v>
@@ -28169,7 +28166,7 @@
         <v>143</v>
       </c>
       <c r="DA87" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB87" t="s">
         <v>130</v>
@@ -28181,7 +28178,7 @@
         <v>173</v>
       </c>
       <c r="DE87" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF87" t="s">
         <v>130</v>
@@ -28219,7 +28216,7 @@
         <v>18</v>
       </c>
       <c r="G88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H88" t="s">
         <v>118</v>
@@ -28303,7 +28300,7 @@
         <v>0</v>
       </c>
       <c r="AQ88" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AR88" t="s">
         <v>164</v>
@@ -28342,7 +28339,7 @@
         <v>116</v>
       </c>
       <c r="BD88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BE88" t="s">
         <v>167</v>
@@ -28391,7 +28388,7 @@
       <c r="BU88"/>
       <c r="BV88"/>
       <c r="BW88" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX88" t="s">
         <v>131</v>
@@ -28493,7 +28490,7 @@
         <v>145</v>
       </c>
       <c r="DE88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF88" t="s">
         <v>130</v>
@@ -28699,7 +28696,7 @@
       <c r="BU89"/>
       <c r="BV89"/>
       <c r="BW89" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX89" t="s">
         <v>130</v>
@@ -28801,7 +28798,7 @@
         <v>173</v>
       </c>
       <c r="DE89" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF89" t="s">
         <v>130</v>
@@ -28872,7 +28869,7 @@
       <c r="V90"/>
       <c r="W90"/>
       <c r="X90" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y90" t="n">
         <v>11</v>
@@ -29109,7 +29106,7 @@
         <v>173</v>
       </c>
       <c r="DE90" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF90" t="s">
         <v>130</v>
@@ -29227,7 +29224,7 @@
         <v>116</v>
       </c>
       <c r="AO91" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP91" t="n">
         <v>1</v>
@@ -29317,7 +29314,7 @@
       <c r="BU91"/>
       <c r="BV91"/>
       <c r="BW91" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX91" t="s">
         <v>130</v>
@@ -29419,7 +29416,7 @@
         <v>173</v>
       </c>
       <c r="DE91" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF91" t="s">
         <v>130</v>
@@ -29629,7 +29626,7 @@
       <c r="BU92"/>
       <c r="BV92"/>
       <c r="BW92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX92" t="s">
         <v>130</v>
@@ -29731,7 +29728,7 @@
         <v>173</v>
       </c>
       <c r="DE92" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF92" t="s">
         <v>130</v>
@@ -29835,7 +29832,7 @@
         <v>114</v>
       </c>
       <c r="AK93" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL93"/>
       <c r="AM93" t="s">
@@ -29927,7 +29924,7 @@
         <v>169</v>
       </c>
       <c r="BS93" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT93" t="s">
         <v>158</v>
@@ -29935,7 +29932,7 @@
       <c r="BU93"/>
       <c r="BV93"/>
       <c r="BW93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX93" t="s">
         <v>131</v>
@@ -30143,7 +30140,7 @@
         <v>114</v>
       </c>
       <c r="AK94" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL94" t="n">
         <v>3</v>
@@ -30353,7 +30350,7 @@
         <v>173</v>
       </c>
       <c r="DE94" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF94" t="s">
         <v>130</v>
@@ -30477,7 +30474,7 @@
         <v>1</v>
       </c>
       <c r="AQ95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AR95" t="s">
         <v>164</v>
@@ -30555,7 +30552,7 @@
         <v>134</v>
       </c>
       <c r="BS95" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BT95" t="s">
         <v>136</v>
@@ -30563,7 +30560,7 @@
       <c r="BU95"/>
       <c r="BV95"/>
       <c r="BW95" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX95" t="s">
         <v>131</v>
@@ -30665,7 +30662,7 @@
         <v>145</v>
       </c>
       <c r="DE95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF95" t="s">
         <v>130</v>
@@ -30778,7 +30775,7 @@
         <v>116</v>
       </c>
       <c r="AN96" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AO96" t="s">
         <v>123</v>
@@ -30787,7 +30784,7 @@
         <v>1</v>
       </c>
       <c r="AQ96" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR96" t="s">
         <v>164</v>
@@ -30824,7 +30821,7 @@
         <v>114</v>
       </c>
       <c r="BD96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BE96" t="s">
         <v>116</v>
@@ -30873,7 +30870,7 @@
       <c r="BU96"/>
       <c r="BV96"/>
       <c r="BW96" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX96" t="s">
         <v>130</v>
@@ -30957,13 +30954,13 @@
         <v>141</v>
       </c>
       <c r="CY96" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CZ96" t="s">
         <v>143</v>
       </c>
       <c r="DA96" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB96" t="s">
         <v>130</v>
@@ -31004,7 +31001,7 @@
         <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E97" t="s">
         <v>116</v>
@@ -31081,7 +31078,7 @@
         <v>114</v>
       </c>
       <c r="AK97" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL97" t="n">
         <v>1</v>
@@ -31285,7 +31282,7 @@
         <v>145</v>
       </c>
       <c r="DE97" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF97" t="s">
         <v>130</v>
@@ -31391,7 +31388,7 @@
         <v>114</v>
       </c>
       <c r="AK98" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL98" t="n">
         <v>12</v>
@@ -31497,7 +31494,7 @@
         <v>11</v>
       </c>
       <c r="BW98" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX98" t="s">
         <v>130</v>
@@ -31655,7 +31652,7 @@
       <c r="M99"/>
       <c r="N99"/>
       <c r="O99" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P99" t="s">
         <v>114</v>
@@ -31703,7 +31700,7 @@
         <v>114</v>
       </c>
       <c r="AK99" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AL99"/>
       <c r="AM99" t="s">
@@ -31909,7 +31906,7 @@
         <v>173</v>
       </c>
       <c r="DE99" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF99" t="s">
         <v>130</v>
@@ -32015,7 +32012,7 @@
         <v>114</v>
       </c>
       <c r="AK100" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL100" t="n">
         <v>36</v>
@@ -32375,7 +32372,7 @@
         <v>116</v>
       </c>
       <c r="BE101" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BF101" t="n">
         <v>14</v>
@@ -32421,7 +32418,7 @@
       <c r="BU101"/>
       <c r="BV101"/>
       <c r="BW101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX101" t="s">
         <v>131</v>
@@ -32523,7 +32520,7 @@
         <v>145</v>
       </c>
       <c r="DE101" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF101" t="s">
         <v>130</v>
@@ -32627,7 +32624,7 @@
         <v>114</v>
       </c>
       <c r="AK102" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL102" t="n">
         <v>72</v>
@@ -32729,7 +32726,7 @@
       <c r="BU102"/>
       <c r="BV102"/>
       <c r="BW102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX102" t="s">
         <v>130</v>
@@ -32831,7 +32828,7 @@
         <v>145</v>
       </c>
       <c r="DE102" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF102" t="s">
         <v>130</v>
@@ -33141,7 +33138,7 @@
         <v>173</v>
       </c>
       <c r="DE103" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF103" t="s">
         <v>130</v>
@@ -33263,7 +33260,7 @@
         <v>1</v>
       </c>
       <c r="AQ104" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AR104" t="s">
         <v>164</v>
@@ -33349,7 +33346,7 @@
       <c r="BU104"/>
       <c r="BV104"/>
       <c r="BW104" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX104" t="s">
         <v>130</v>
@@ -33451,7 +33448,7 @@
         <v>145</v>
       </c>
       <c r="DE104" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF104" t="s">
         <v>130</v>
@@ -33606,7 +33603,7 @@
         <v>131</v>
       </c>
       <c r="BB105" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC105" t="s">
         <v>116</v>
@@ -33615,7 +33612,7 @@
         <v>116</v>
       </c>
       <c r="BE105" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BF105" t="n">
         <v>9</v>
@@ -33765,7 +33762,7 @@
         <v>173</v>
       </c>
       <c r="DE105" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF105" t="s">
         <v>130</v>
@@ -33836,7 +33833,7 @@
       <c r="V106"/>
       <c r="W106"/>
       <c r="X106" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y106" t="n">
         <v>11</v>
@@ -33878,14 +33875,14 @@
         <v>116</v>
       </c>
       <c r="AN106" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AO106" t="s">
         <v>123</v>
       </c>
       <c r="AP106"/>
       <c r="AQ106" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR106" t="s">
         <v>164</v>
@@ -33969,7 +33966,7 @@
       <c r="BU106"/>
       <c r="BV106"/>
       <c r="BW106" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX106" t="s">
         <v>131</v>
@@ -34053,13 +34050,13 @@
         <v>141</v>
       </c>
       <c r="CY106" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CZ106" t="s">
         <v>143</v>
       </c>
       <c r="DA106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB106" t="s">
         <v>130</v>
@@ -34071,7 +34068,7 @@
         <v>145</v>
       </c>
       <c r="DE106" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF106" t="s">
         <v>130</v>
@@ -34231,7 +34228,7 @@
         <v>116</v>
       </c>
       <c r="BE107" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="BF107" t="n">
         <v>8</v>
@@ -34277,7 +34274,7 @@
       <c r="BU107"/>
       <c r="BV107"/>
       <c r="BW107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX107" t="s">
         <v>131</v>
@@ -34365,7 +34362,7 @@
         <v>143</v>
       </c>
       <c r="DA107" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB107" t="s">
         <v>130</v>
@@ -34377,7 +34374,7 @@
         <v>145</v>
       </c>
       <c r="DE107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF107" t="s">
         <v>130</v>
@@ -34473,7 +34470,7 @@
         <v>114</v>
       </c>
       <c r="AG108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH108"/>
       <c r="AI108"/>
@@ -34539,7 +34536,7 @@
         <v>116</v>
       </c>
       <c r="BE108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BF108" t="n">
         <v>4</v>
@@ -34687,7 +34684,7 @@
         <v>145</v>
       </c>
       <c r="DE108" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF108" t="s">
         <v>130</v>
@@ -34891,7 +34888,7 @@
       <c r="BU109"/>
       <c r="BV109"/>
       <c r="BW109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX109" t="s">
         <v>130</v>
@@ -34981,7 +34978,7 @@
         <v>143</v>
       </c>
       <c r="DA109" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB109" t="s">
         <v>130</v>
@@ -34993,7 +34990,7 @@
         <v>173</v>
       </c>
       <c r="DE109" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF109" t="s">
         <v>130</v>
@@ -35113,7 +35110,7 @@
       </c>
       <c r="AP110"/>
       <c r="AQ110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AR110" t="s">
         <v>164</v>
@@ -35146,7 +35143,7 @@
         <v>131</v>
       </c>
       <c r="BB110" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC110" t="s">
         <v>116</v>
@@ -35297,7 +35294,7 @@
         <v>145</v>
       </c>
       <c r="DE110" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF110" t="s">
         <v>130</v>
@@ -35419,7 +35416,7 @@
       </c>
       <c r="AP111"/>
       <c r="AQ111" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AR111" t="s">
         <v>164</v>
@@ -35456,10 +35453,10 @@
         <v>116</v>
       </c>
       <c r="BD111" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BE111" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BF111" t="n">
         <v>6</v>
@@ -35505,7 +35502,7 @@
       <c r="BU111"/>
       <c r="BV111"/>
       <c r="BW111" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX111" t="s">
         <v>130</v>
@@ -35595,7 +35592,7 @@
         <v>143</v>
       </c>
       <c r="DA111" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB111" t="s">
         <v>130</v>
@@ -35607,7 +35604,7 @@
         <v>145</v>
       </c>
       <c r="DE111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF111" t="s">
         <v>130</v>
@@ -35817,7 +35814,7 @@
         <v>5</v>
       </c>
       <c r="BW112" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX112" t="s">
         <v>131</v>
@@ -35919,7 +35916,7 @@
         <v>145</v>
       </c>
       <c r="DE112" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF112" t="s">
         <v>130</v>
@@ -36123,7 +36120,7 @@
       <c r="BU113"/>
       <c r="BV113"/>
       <c r="BW113" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX113" t="s">
         <v>131</v>
@@ -36213,7 +36210,7 @@
         <v>143</v>
       </c>
       <c r="DA113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB113" t="s">
         <v>130</v>
@@ -36225,7 +36222,7 @@
         <v>173</v>
       </c>
       <c r="DE113" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF113" t="s">
         <v>130</v>
@@ -36331,7 +36328,7 @@
         <v>114</v>
       </c>
       <c r="AK114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL114" t="n">
         <v>1</v>
@@ -36349,7 +36346,7 @@
         <v>1</v>
       </c>
       <c r="AQ114" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR114" t="s">
         <v>164</v>
@@ -37047,7 +37044,7 @@
       <c r="BU116"/>
       <c r="BV116"/>
       <c r="BW116" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX116" t="s">
         <v>131</v>
@@ -37149,7 +37146,7 @@
         <v>173</v>
       </c>
       <c r="DE116" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF116" t="s">
         <v>130</v>
@@ -37274,7 +37271,7 @@
       </c>
       <c r="AS117"/>
       <c r="AT117" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU117" t="s">
         <v>127</v>
@@ -37305,7 +37302,7 @@
         <v>116</v>
       </c>
       <c r="BE117" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BF117" t="n">
         <v>4</v>
@@ -37351,7 +37348,7 @@
       <c r="BU117"/>
       <c r="BV117"/>
       <c r="BW117" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX117" t="s">
         <v>131</v>
@@ -37441,7 +37438,7 @@
         <v>143</v>
       </c>
       <c r="DA117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB117" t="s">
         <v>130</v>
@@ -37453,7 +37450,7 @@
         <v>145</v>
       </c>
       <c r="DE117" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF117" t="s">
         <v>130</v>
@@ -37557,7 +37554,7 @@
         <v>114</v>
       </c>
       <c r="AK118" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AL118" t="n">
         <v>24</v>
@@ -37573,7 +37570,7 @@
       </c>
       <c r="AP118"/>
       <c r="AQ118" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AR118" t="s">
         <v>164</v>
@@ -37657,7 +37654,7 @@
       <c r="BU118"/>
       <c r="BV118"/>
       <c r="BW118" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX118" t="s">
         <v>131</v>
@@ -37759,7 +37756,7 @@
         <v>173</v>
       </c>
       <c r="DE118" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF118" t="s">
         <v>130</v>
@@ -37881,14 +37878,14 @@
         <v>2</v>
       </c>
       <c r="AQ119" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AR119" t="s">
         <v>164</v>
       </c>
       <c r="AS119"/>
       <c r="AT119" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU119" t="s">
         <v>127</v>
@@ -37919,7 +37916,7 @@
         <v>116</v>
       </c>
       <c r="BE119" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BF119" t="n">
         <v>2</v>
@@ -37965,7 +37962,7 @@
       <c r="BU119"/>
       <c r="BV119"/>
       <c r="BW119" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX119" t="s">
         <v>131</v>
@@ -38067,7 +38064,7 @@
         <v>173</v>
       </c>
       <c r="DE119" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF119" t="s">
         <v>130</v>
@@ -38191,14 +38188,14 @@
         <v>4</v>
       </c>
       <c r="AQ120" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR120" t="s">
         <v>164</v>
       </c>
       <c r="AS120"/>
       <c r="AT120" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU120" t="s">
         <v>127</v>
@@ -38226,7 +38223,7 @@
         <v>116</v>
       </c>
       <c r="BD120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BE120" t="s">
         <v>114</v>
@@ -38359,7 +38356,7 @@
         <v>143</v>
       </c>
       <c r="DA120" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB120" t="s">
         <v>130</v>
@@ -38371,7 +38368,7 @@
         <v>173</v>
       </c>
       <c r="DE120" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF120" t="s">
         <v>130</v>
@@ -38493,7 +38490,7 @@
         <v>1</v>
       </c>
       <c r="AQ121" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AR121" t="s">
         <v>125</v>
@@ -38579,7 +38576,7 @@
       <c r="BU121"/>
       <c r="BV121"/>
       <c r="BW121" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX121" t="s">
         <v>130</v>
@@ -38681,7 +38678,7 @@
         <v>145</v>
       </c>
       <c r="DE121" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF121" t="s">
         <v>130</v>
@@ -38803,7 +38800,7 @@
       </c>
       <c r="AP122"/>
       <c r="AQ122" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR122" t="s">
         <v>164</v>
@@ -38977,7 +38974,7 @@
         <v>143</v>
       </c>
       <c r="DA122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB122" t="s">
         <v>130</v>
@@ -38989,7 +38986,7 @@
         <v>145</v>
       </c>
       <c r="DE122" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF122" t="s">
         <v>130</v>
@@ -39060,7 +39057,7 @@
       <c r="V123"/>
       <c r="W123"/>
       <c r="X123" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y123" t="n">
         <v>11</v>
@@ -39120,7 +39117,7 @@
       </c>
       <c r="AS123"/>
       <c r="AT123" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU123" t="s">
         <v>127</v>
@@ -39299,7 +39296,7 @@
         <v>145</v>
       </c>
       <c r="DE123" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF123" t="s">
         <v>130</v>
@@ -39428,7 +39425,7 @@
       </c>
       <c r="AS124"/>
       <c r="AT124" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU124" t="s">
         <v>127</v>
@@ -39456,7 +39453,7 @@
         <v>116</v>
       </c>
       <c r="BD124" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BE124" t="s">
         <v>114</v>
@@ -39503,7 +39500,7 @@
       <c r="BU124"/>
       <c r="BV124"/>
       <c r="BW124" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX124" t="s">
         <v>130</v>
@@ -39605,7 +39602,7 @@
         <v>145</v>
       </c>
       <c r="DE124" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF124" t="s">
         <v>130</v>
@@ -39701,7 +39698,7 @@
         <v>114</v>
       </c>
       <c r="AG125" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH125"/>
       <c r="AI125"/>
@@ -40007,7 +40004,7 @@
         <v>114</v>
       </c>
       <c r="AG126" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH126"/>
       <c r="AI126"/>
@@ -40015,7 +40012,7 @@
         <v>114</v>
       </c>
       <c r="AK126" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL126" t="n">
         <v>12</v>
@@ -40033,10 +40030,10 @@
         <v>4</v>
       </c>
       <c r="AQ126" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AR126" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS126"/>
       <c r="AT126" t="s">
@@ -40071,7 +40068,7 @@
         <v>116</v>
       </c>
       <c r="BE126" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BF126" t="n">
         <v>20</v>
@@ -40121,7 +40118,7 @@
         <v>15</v>
       </c>
       <c r="BW126" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX126" t="s">
         <v>131</v>
@@ -40347,7 +40344,7 @@
         <v>1</v>
       </c>
       <c r="AQ127" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AR127" t="s">
         <v>164</v>
@@ -40385,7 +40382,7 @@
         <v>116</v>
       </c>
       <c r="BE127" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="BF127" t="n">
         <v>24</v>
@@ -40521,7 +40518,7 @@
         <v>143</v>
       </c>
       <c r="DA127" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB127" t="s">
         <v>130</v>
@@ -40692,7 +40689,7 @@
         <v>116</v>
       </c>
       <c r="BD128" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BE128" t="s">
         <v>118</v>
@@ -40745,7 +40742,7 @@
         <v>22</v>
       </c>
       <c r="BW128" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX128" t="s">
         <v>130</v>
@@ -40835,7 +40832,7 @@
         <v>143</v>
       </c>
       <c r="DA128" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB128" t="s">
         <v>130</v>
@@ -40847,7 +40844,7 @@
         <v>145</v>
       </c>
       <c r="DE128" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF128" t="s">
         <v>130</v>
@@ -40943,7 +40940,7 @@
         <v>114</v>
       </c>
       <c r="AG129" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH129"/>
       <c r="AI129"/>
@@ -40967,7 +40964,7 @@
       </c>
       <c r="AP129"/>
       <c r="AQ129" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AR129" t="s">
         <v>164</v>
@@ -40998,7 +40995,7 @@
         <v>131</v>
       </c>
       <c r="BB129" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC129" t="s">
         <v>116</v>
@@ -41147,7 +41144,7 @@
         <v>143</v>
       </c>
       <c r="DA129" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB129" t="s">
         <v>130</v>
@@ -41159,7 +41156,7 @@
         <v>145</v>
       </c>
       <c r="DE129" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF129" t="s">
         <v>130</v>
@@ -41281,7 +41278,7 @@
         <v>1</v>
       </c>
       <c r="AQ130" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AR130" t="s">
         <v>164</v>
@@ -41290,7 +41287,7 @@
         <v>116</v>
       </c>
       <c r="AT130" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU130" t="s">
         <v>127</v>
@@ -41321,7 +41318,7 @@
         <v>177</v>
       </c>
       <c r="BE130" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BF130" t="n">
         <v>2</v>
@@ -41367,7 +41364,7 @@
       <c r="BU130"/>
       <c r="BV130"/>
       <c r="BW130" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX130" t="s">
         <v>130</v>
@@ -41457,7 +41454,7 @@
         <v>143</v>
       </c>
       <c r="DA130" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB130" t="s">
         <v>131</v>
@@ -41565,7 +41562,7 @@
         <v>114</v>
       </c>
       <c r="AG131" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH131"/>
       <c r="AI131"/>
@@ -41591,14 +41588,14 @@
         <v>1</v>
       </c>
       <c r="AQ131" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AR131" t="s">
         <v>164</v>
       </c>
       <c r="AS131"/>
       <c r="AT131" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="AU131" t="s">
         <v>127</v>
@@ -41629,7 +41626,7 @@
         <v>150</v>
       </c>
       <c r="BE131" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BF131" t="n">
         <v>9</v>
@@ -41675,7 +41672,7 @@
       <c r="BU131"/>
       <c r="BV131"/>
       <c r="BW131" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX131" t="s">
         <v>130</v>
@@ -41869,7 +41866,7 @@
         <v>114</v>
       </c>
       <c r="AG132" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH132"/>
       <c r="AI132"/>
@@ -41932,10 +41929,10 @@
         <v>124</v>
       </c>
       <c r="BD132" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BE132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BF132" t="n">
         <v>6</v>
@@ -42071,7 +42068,7 @@
         <v>143</v>
       </c>
       <c r="DA132" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB132" t="s">
         <v>130</v>
@@ -42207,10 +42204,10 @@
         <v>1</v>
       </c>
       <c r="AQ133" t="s">
+        <v>206</v>
+      </c>
+      <c r="AR133" t="s">
         <v>207</v>
-      </c>
-      <c r="AR133" t="s">
-        <v>208</v>
       </c>
       <c r="AS133" t="s">
         <v>116</v>
@@ -42246,7 +42243,7 @@
         <v>114</v>
       </c>
       <c r="BD133" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BE133" t="s">
         <v>127</v>
@@ -42295,7 +42292,7 @@
       <c r="BU133"/>
       <c r="BV133"/>
       <c r="BW133" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BX133" t="s">
         <v>131</v>
@@ -42385,7 +42382,7 @@
         <v>143</v>
       </c>
       <c r="DA133" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB133" t="s">
         <v>130</v>
@@ -42493,7 +42490,7 @@
         <v>114</v>
       </c>
       <c r="AG134" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH134"/>
       <c r="AI134"/>
@@ -42513,11 +42510,11 @@
         <v>124</v>
       </c>
       <c r="AO134" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP134"/>
       <c r="AQ134" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AR134" t="s">
         <v>164</v>
@@ -42548,7 +42545,7 @@
         <v>131</v>
       </c>
       <c r="BB134" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC134" t="s">
         <v>116</v>
@@ -42705,7 +42702,7 @@
         <v>145</v>
       </c>
       <c r="DE134" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF134" t="s">
         <v>130</v>
@@ -42811,7 +42808,7 @@
         <v>114</v>
       </c>
       <c r="AK135" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AL135" t="n">
         <v>12</v>
@@ -42862,7 +42859,7 @@
         <v>131</v>
       </c>
       <c r="BB135" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC135" t="s">
         <v>116</v>
@@ -43019,7 +43016,7 @@
         <v>145</v>
       </c>
       <c r="DE135" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="DF135" t="s">
         <v>130</v>
@@ -43115,7 +43112,7 @@
         <v>114</v>
       </c>
       <c r="AG136" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH136"/>
       <c r="AI136"/>
@@ -43150,7 +43147,7 @@
         <v>116</v>
       </c>
       <c r="AT136" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="AU136" t="s">
         <v>127</v>
@@ -43178,7 +43175,7 @@
         <v>114</v>
       </c>
       <c r="BD136" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BE136" t="s">
         <v>116</v>
@@ -43227,7 +43224,7 @@
       <c r="BU136"/>
       <c r="BV136"/>
       <c r="BW136" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BX136" t="s">
         <v>130</v>
@@ -43317,7 +43314,7 @@
         <v>143</v>
       </c>
       <c r="DA136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DB136" t="s">
         <v>130</v>
@@ -43360,13 +43357,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" t="s">
         <v>277</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>278</v>
-      </c>
-      <c r="C1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="2">
@@ -43374,10 +43371,10 @@
         <v>76</v>
       </c>
       <c r="B2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" t="s">
         <v>280</v>
-      </c>
-      <c r="C2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -43385,10 +43382,10 @@
         <v>77</v>
       </c>
       <c r="B3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C3" t="s">
         <v>282</v>
-      </c>
-      <c r="C3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="4">
@@ -43396,10 +43393,10 @@
         <v>105</v>
       </c>
       <c r="B4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" t="s">
         <v>284</v>
-      </c>
-      <c r="C4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="5">
@@ -43407,10 +43404,10 @@
         <v>106</v>
       </c>
       <c r="B5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" t="s">
         <v>286</v>
-      </c>
-      <c r="C5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="6">
@@ -43421,7 +43418,7 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -43429,10 +43426,10 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" t="s">
         <v>289</v>
-      </c>
-      <c r="C7" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -43440,10 +43437,10 @@
         <v>103</v>
       </c>
       <c r="B8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" t="s">
         <v>291</v>
-      </c>
-      <c r="C8" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -43451,10 +43448,10 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" t="s">
         <v>293</v>
-      </c>
-      <c r="C9" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -43465,7 +43462,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11">
@@ -43476,7 +43473,7 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12">
@@ -43487,7 +43484,7 @@
         <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13">
@@ -43498,7 +43495,7 @@
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
@@ -43509,7 +43506,7 @@
         <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -43520,7 +43517,7 @@
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
@@ -43528,87 +43525,87 @@
         <v>97</v>
       </c>
       <c r="B16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" t="s">
         <v>301</v>
-      </c>
-      <c r="C16" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B17" t="s">
         <v>303</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>304</v>
-      </c>
-      <c r="C17" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B18" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" t="s">
         <v>306</v>
-      </c>
-      <c r="B18" t="s">
-        <v>304</v>
-      </c>
-      <c r="C18" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B19" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" t="s">
         <v>308</v>
-      </c>
-      <c r="B19" t="s">
-        <v>304</v>
-      </c>
-      <c r="C19" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" t="s">
         <v>310</v>
-      </c>
-      <c r="B20" t="s">
-        <v>304</v>
-      </c>
-      <c r="C20" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" t="s">
         <v>312</v>
-      </c>
-      <c r="B21" t="s">
-        <v>304</v>
-      </c>
-      <c r="C21" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B22" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" t="s">
         <v>314</v>
-      </c>
-      <c r="B22" t="s">
-        <v>304</v>
-      </c>
-      <c r="C22" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>315</v>
+      </c>
+      <c r="B23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C23" t="s">
         <v>316</v>
-      </c>
-      <c r="B23" t="s">
-        <v>304</v>
-      </c>
-      <c r="C23" t="s">
-        <v>317</v>
       </c>
     </row>
   </sheetData>
